--- a/example.xlsx
+++ b/example.xlsx
@@ -16,11 +16,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>application_date</t>
   </si>
   <si>
+    <t>date</t>
+  </si>
+  <si>
     <t>company</t>
   </si>
   <si>
@@ -39,12 +42,27 @@
     <t>experience</t>
   </si>
   <si>
+    <t>salary_range</t>
+  </si>
+  <si>
     <t>requested_salary</t>
   </si>
   <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>response_date</t>
+  </si>
+  <si>
     <t>response</t>
   </si>
   <si>
+    <t>observation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunday, 10 May 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Company 1</t>
   </si>
   <si>
@@ -63,6 +81,9 @@
     <t xml:space="preserve">1 year</t>
   </si>
   <si>
+    <t>NO_RESPONSE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Company 2</t>
   </si>
   <si>
@@ -81,6 +102,9 @@
     <t xml:space="preserve">2 years</t>
   </si>
   <si>
+    <t>APPLIED</t>
+  </si>
+  <si>
     <t xml:space="preserve">Company 3</t>
   </si>
   <si>
@@ -88,6 +112,9 @@
   </si>
   <si>
     <t xml:space="preserve">Description 3</t>
+  </si>
+  <si>
+    <t>INTERVIEW</t>
   </si>
   <si>
     <t xml:space="preserve">Company 4</t>
@@ -213,12 +240,15 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -723,274 +753,331 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="1" max="1" width="15.47265625"/>
-    <col min="2" max="2" width="15.47265625"/>
+    <col bestFit="1" min="2" max="2" width="19.09375"/>
     <col customWidth="1" min="3" max="3" width="13.00390625"/>
     <col bestFit="1" min="4" max="4" width="10.04296875"/>
     <col bestFit="1" min="5" max="5" width="14.23046875"/>
     <col bestFit="1" min="6" max="6" width="6.8125"/>
     <col bestFit="1" min="7" max="7" width="14.23046875"/>
     <col bestFit="1" min="8" max="8" width="10.23046875"/>
-    <col bestFit="1" min="9" max="9" width="15.76171875"/>
+    <col bestFit="1" min="9" max="9" width="11.8515625"/>
+    <col bestFit="1" min="10" max="10" width="15.76171875"/>
+    <col bestFit="1" min="11" max="11" width="13.47265625"/>
+    <col min="12" max="12" width="15.76171875"/>
+    <col bestFit="1" min="14" max="14" width="11.09375"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="2">
-        <f t="shared" ref="A2:A10" ca="1" si="0">TODAY()</f>
-        <v>46073</v>
-      </c>
-      <c r="B2" s="3"/>
+        <f ca="1">TODAY()</f>
+        <v>46152</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="K2" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <f t="shared" ref="A3:A10" ca="1" si="0">TODAY()</f>
+        <v>46152</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>16</v>
+      <c r="C3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="K3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46152</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
+      <c r="C4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="K4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46152</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>27</v>
+      <c r="G5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="K5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46152</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="K6" t="s">
         <v>28</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46152</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
+      <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="K7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46152</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>36</v>
+      <c r="C8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="K8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46152</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>39</v>
+      <c r="C9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="K9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46152</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>42</v>
+      <c r="C10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="K10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="F11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="F11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
